--- a/Result/profitability/6929.xlsx
+++ b/Result/profitability/6929.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AM20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2843,6 +2843,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6929</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>803</v>
+      </c>
+      <c r="D20" t="n">
+        <v>539</v>
+      </c>
+      <c r="E20" t="n">
+        <v>264</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.42625</v>
+      </c>
+      <c r="N20" t="n">
+        <v>32.98125</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.5238095238095239</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.2800000000000011</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.008441362677117925</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.6799999999999997</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.02025618111409</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
